--- a/AAII_Financials/Quarterly/GSK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GSK_QTR_FIN.xlsx
@@ -656,540 +656,553 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>11157000</v>
+      </c>
+      <c r="E8" s="3">
         <v>10073900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>11598900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>11488800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10941200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9710700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10161900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10738500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9963700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9299300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10256300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9941900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9121800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8599300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9678800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10018100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>8835200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8919900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>8967400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8222800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6961900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6147400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>10337400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10547300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9938600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12099700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12136400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13280800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10723200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10199900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10826500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>9966100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>9450400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9336700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>9963600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>10229700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>9547500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9723200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9989200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>9931200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2749100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2473200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3522200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3009700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2966200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2488400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3176100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3120200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2605900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2418600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2978000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2737200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2413200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2354300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2856700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3053100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2723600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3337200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3499000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2434400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2007000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1908000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3503700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3315700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3166400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3701800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4106400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4211400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3338200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3160700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3523900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3104900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2853200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2996700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3122500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3183800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2778200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3097100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3066800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3216900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>8407900</v>
+      </c>
+      <c r="E10" s="3">
         <v>7600600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8076700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8479200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7975100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7222300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6985700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7618300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7357800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6880700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7278200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>7204700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6708500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6245100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6822100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6964900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6111600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5582700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5468400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5788300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4954900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>4239400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6833600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7231600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6772200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8397900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8030000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9069400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7385000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7039100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7302600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6861200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6597200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>6339900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>6841100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7045900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6769400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>6626100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>6922400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>6714300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,130 +1245,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2317900</v>
+      </c>
+      <c r="E12" s="3">
         <v>2004500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>2877500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2117100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2115400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1804900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2298500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1931400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1804700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1734100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2292800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1767000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1696500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1534000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1997200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1659700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1472700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1349800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1628500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1379800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1318900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>1218700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1534200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>1279700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>1526500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>1445600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1587500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1647200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1428100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1292800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1345900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1183600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1122200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1146700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>1293900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>1171300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>1373400</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>1210100</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>1339200</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>1153500</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,252 +1493,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>2814100</v>
+      </c>
+      <c r="E14" s="3">
         <v>627200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>714700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>657300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>505500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>121400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>376800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>642000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>635700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>958600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1436800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>995800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-175400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-193000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-572100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1556000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>937200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-492500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>966900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>884700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>338700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-48900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>662400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>746600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-1686800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>629600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-312300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>615600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>656400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>728300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>488700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>570200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1529400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>686500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>1712600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>566100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>2504300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>156700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>1663100</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>863800</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>295900</v>
+      </c>
+      <c r="E15" s="3">
         <v>611400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1424000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>992000</v>
       </c>
-      <c r="G15" s="3">
-        <v>1587900</v>
-      </c>
       <c r="H15" s="3">
+        <v>848100</v>
+      </c>
+      <c r="I15" s="3">
         <v>1063300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1059100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1274600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>807600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>693400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>293000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>706600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>574400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>791800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>21000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>33300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>33200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>28500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>32300</v>
-      </c>
-      <c r="W15" s="3">
-        <v>29800</v>
       </c>
       <c r="X15" s="3">
         <v>29800</v>
       </c>
       <c r="Y15" s="3">
+        <v>29800</v>
+      </c>
+      <c r="Z15" s="3">
         <v>30800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>19500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>22200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>22600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>21800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>19800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>23300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>22600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>18500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>12300</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>12900</v>
       </c>
       <c r="AJ15" s="3">
         <v>12900</v>
       </c>
       <c r="AK15" s="3">
+        <v>12900</v>
+      </c>
+      <c r="AL15" s="3">
         <v>14300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>15700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>14300</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>14500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>13200</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1787,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7704700</v>
+      </c>
+      <c r="E17" s="3">
         <v>6418800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9403800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7346000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7664100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6726200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8906200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9844500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7247800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6461400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8089600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6567700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6577600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6220300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7227600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8494100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7456800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6075200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8343900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6510500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5484400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4704500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9082300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8280700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6223300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9418900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>9542400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10242600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>8685400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>8298600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8774000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7610100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>8443300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>7733600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9209700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>7771100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>9547500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>7460900</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>9205700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>8046900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3452300</v>
+      </c>
+      <c r="E18" s="3">
         <v>3655100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2195200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4142800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3277200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2984500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1255700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>894000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2715900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2837900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2166700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3374200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2544100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2379000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2451200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1524000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1378400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2844700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>623500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1712300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1477500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1442900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1255100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2266600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3715200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2680800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2593900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3038200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2037800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1901200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2052500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2356100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1007100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1603100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>753900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2458600</v>
       </c>
-      <c r="AM18" s="3">
-        <v>0</v>
-      </c>
       <c r="AN18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="3">
         <v>2262200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>783500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1884300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,31 +2082,32 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>5300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>29600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2700</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>78900</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1300</v>
       </c>
       <c r="K20" s="3">
         <v>1300</v>
@@ -2082,269 +2116,275 @@
         <v>1300</v>
       </c>
       <c r="M20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N20" s="3">
         <v>95500</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="O20" s="3">
-        <v>2500</v>
       </c>
       <c r="P20" s="3">
         <v>2500</v>
       </c>
       <c r="Q20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R20" s="3">
         <v>-317600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-229100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-235900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-246900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-239500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-233300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-201500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-209900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-283900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-228100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-272500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-238300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-260500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-277400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-302100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-177100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-237700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-256200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-213300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-171900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-177400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-226900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-232200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-221200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-226500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-206700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3744200</v>
+      </c>
+      <c r="E21" s="3">
         <v>4261200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3589500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5140200</v>
       </c>
-      <c r="G21" s="3">
-        <v>4862300</v>
-      </c>
       <c r="H21" s="3">
+        <v>4122500</v>
+      </c>
+      <c r="I21" s="3">
         <v>4047900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2235900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2167300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3522200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3530000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2364100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4080700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3116000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3168300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2144100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2518300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1947100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3471200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1282500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2606900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1925900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1663600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3522700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>2034800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3446700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2700800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2145200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3486800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2801300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3299200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2722100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2710800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1045900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2049100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>348300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3123800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1185600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2470300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1378700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1929100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>241500</v>
+      </c>
+      <c r="E22" s="3">
         <v>220500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>195200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>224500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>252100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>209300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>150200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>207700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>219900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>207100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>179600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>222100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>233800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>246200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>24</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>24</v>
@@ -2355,8 +2395,8 @@
       <c r="V22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2415,252 +2455,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>469700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2831100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1278600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3301300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2585300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2723500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>704800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>85800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1889400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1711300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>482800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2185600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2525100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2359200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2133600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1295000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1142500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2597800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>384000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1479000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1276000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1233100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>971200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2038500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3442800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2442600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2333400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2760900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1735700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1724200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1814800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2099900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>793800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1431100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>576500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2231700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-232200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2041000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>557000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1677600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-264000</v>
+      </c>
+      <c r="E24" s="3">
         <v>402700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>419400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>330200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>434100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>77600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>241400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>346100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-24200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>313600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>307500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>341400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>298100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>191300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-148300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>305200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-239700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>184800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-21300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>294000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>262000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>207700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>264600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>332600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>293900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>412700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>262800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>237700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>179700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>449900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-356100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>412200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>-120000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>430600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>139600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>512200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2830,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>733700</v>
+      </c>
+      <c r="E26" s="3">
         <v>2428300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>978500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2882000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2255100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2289400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>627200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>87100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1648000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1365300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>507000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1872000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2217500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2017800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2132300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>996800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>951200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2197100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>532300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1173800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1515700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1048200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>992500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1744500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3180800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2234900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2068900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2428300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1441800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1311400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1551900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1862200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>614100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>981200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>932600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1819500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-112200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1610400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>417400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1165400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>577200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2293700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>856000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2705900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1977000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2098200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>518300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-77700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1482400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1321100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>445800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1786500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2063800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1843300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1968300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>948200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>776500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1744300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>302900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>925600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1345200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>825200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>800800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1517600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2950000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2083200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1771600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2196300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1323800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1105100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1439700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1746400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>570100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>709800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>693900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1580800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-234800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1377400</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>338400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1064000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3205,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3192,37 +3253,37 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>657400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>12251000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>292000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>491300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>646300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>523600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>318400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>454300</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -3239,11 +3300,11 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>165100</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>24</v>
@@ -3251,11 +3312,11 @@
       <c r="AJ29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1406000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3269,8 +3330,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3391,8 +3455,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3513,31 +3580,34 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-5300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-29600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2700</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="I32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-78900</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1300</v>
       </c>
       <c r="K32" s="3">
         <v>-1300</v>
@@ -3546,219 +3616,225 @@
         <v>-1300</v>
       </c>
       <c r="M32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N32" s="3">
         <v>-95500</v>
       </c>
-      <c r="N32" s="3" t="s">
+      <c r="O32" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-2500</v>
       </c>
       <c r="P32" s="3">
         <v>-2500</v>
       </c>
       <c r="Q32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="R32" s="3">
         <v>317600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>229100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>235900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>246900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>239500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>233300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>201500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>209900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>283900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>228100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>272500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>238300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>260500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>277400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>302100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>177100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>237700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>256200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>213300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>171900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>177400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>226900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>232200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>221200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>226500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>206700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>577200</v>
+      </c>
+      <c r="E33" s="3">
         <v>2293700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>856000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2705900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1977000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2098200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>518300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-77700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1482400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1321100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>445800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1786500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2063800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1843300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2625700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13199200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1068500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2235600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>949200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1449300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1663600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1279600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>800800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1517600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2950000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2083200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1771600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2196300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1323800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1105100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1604800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1746400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>570100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>709800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-712200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1580800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-234800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1377400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>338400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1064000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3879,257 +3955,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>577200</v>
+      </c>
+      <c r="E35" s="3">
         <v>2293700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>856000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2705900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1977000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2098200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>518300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-77700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1482400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1321100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>445800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1786500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2063800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1843300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2625700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13199200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1068500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2235600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>949200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1449300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1663600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1279600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>800800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1517600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2950000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2083200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1771600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2196300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1323800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1105100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1604800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1746400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>570100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>709800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-712200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1580800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-234800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1377400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>338400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1064000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4172,8 +4257,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4216,130 +4302,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4119700</v>
+      </c>
+      <c r="E41" s="3">
         <v>4545100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4572000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4430500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4930800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5767500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4844900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4278200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3743300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3523700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3739700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3876900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3990300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3575300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4885300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4614300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8243500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13605700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5416400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4284500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4177400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5672800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7442800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5224800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10645100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>6348000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6419400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6092000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5661700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5501300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5116700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4671500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5230700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>5176400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4999400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6186300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>5199000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>5937400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>6448300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>6075700</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4347,975 +4437,999 @@
         <v>1300</v>
       </c>
       <c r="E42" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F42" s="3">
         <v>32300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>120200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>26800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1648200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3505400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4278400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>4274900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5053700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5450900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4549000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>85400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3734200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>77300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>75700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>70400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>71600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>92300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>101300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>113400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>114500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>107700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>121700</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>115300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>107800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>110900</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>98500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>104700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>98300</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>101700</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>107000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>110900</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>115900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>117200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>111900</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10712500</v>
+      </c>
+      <c r="E43" s="3">
         <v>10480600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9924600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11162200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10545300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9691300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8682100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10544200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>9829800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9208400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8909900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>10829100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9016300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8819500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9786400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10357200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>8759900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>10913600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>10576900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>10278800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8952200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8565800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>9017200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>10272800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>9771700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>11840100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>10179300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11804800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>9696100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>8944300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>8785900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>9297300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>8805300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>8283000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8162400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>8778000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>8337100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>8494600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8232600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9548000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8334900</v>
+      </c>
+      <c r="E44" s="3">
         <v>8130100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7973100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>8223800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>8318900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7752000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7097200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7931900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7404600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7201500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7003100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6687300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7004600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6624900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6752600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5961700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5947100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7447300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7328800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7747600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7548600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7412600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7092700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7856200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8337800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7922700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>8110500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9588800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>8182800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>7559700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>7232600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>7128500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>7683200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>7316000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>7248100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>7383700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>7490700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>7133100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>6718300</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>7075100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>128700</v>
+      </c>
+      <c r="E45" s="3">
         <v>295800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>546400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>153200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>390500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>127900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>46300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>403400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>182000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>147800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>137600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>247700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>301200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>321700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>377900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>428700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>46059200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>261800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>266100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>263000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>199100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>367300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>305200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>797800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1085900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3089500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1764700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2095800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1374600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1218200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1110800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>256200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>210700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>358100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>236100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>573900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>286900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>424000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>488500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>380600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23297100</v>
+      </c>
+      <c r="E46" s="3">
         <v>23452900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23566600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>23983100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24212900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>23365900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21279000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23184600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21186200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21729500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>23747900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25919500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24587300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24395000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>27253100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>25910800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>69095100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>35962500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>23665600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>22649600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20947600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22090100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>23950200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>24252800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>29953900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>29314800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>26581600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>29703200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25030500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>23331500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>22357000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>21452000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>22034700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>21231800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>20747700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>23028900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>21424600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>22105000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>22004900</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>23191300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1267100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1265000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1515500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1455800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1338500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1333400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1497300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1479700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1455900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1612800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1552700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1393600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1715600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1657800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2022100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2085800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2203400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2157400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2805800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3496600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3857800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4477900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4050200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3625500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3342400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2916400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2933500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2725500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2319300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2186200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2057800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1987800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1640600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1484100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1436000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>1455600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>1647300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>1744700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>1643400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1582800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13310300</v>
+      </c>
+      <c r="E48" s="3">
         <v>13254900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13523600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13619400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13588200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12882600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12610600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13034400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12414200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12461800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12682800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11536900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11837400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11646400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12623400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12348200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11671000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13279400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13524600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13235600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>12627500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12680000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13019000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13669000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>14901300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15177200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15429900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16556800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15665400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15034200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14605300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13452800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13992100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13782600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14164800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13868700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>13906600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>14237100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>14231900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>14446500</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>32085700</v>
+      </c>
+      <c r="E49" s="3">
         <v>33573000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>31986500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32236500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>30291800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>29953900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28164600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>29071200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28350600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>28600100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>27486400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>27174000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>28271300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26000800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>28033800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>29154600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22029900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>51079200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>51491700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>50653200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>47423700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>47533400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>47814000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>50689300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>55091000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>56436000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>56620500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>61558700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>37295800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>35720100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>30366300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>28463500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>29827700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>29593700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>30385200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>30892600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>31732600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>32541800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>32578700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>32045400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5436,8 +5550,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5558,130 +5675,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3542500</v>
+      </c>
+      <c r="E52" s="3">
         <v>3142700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2891000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2865800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2738700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2613700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2432500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2605500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2183800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2089000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1983200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1400900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1781700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1850800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8991200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7677700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8541900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8789700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8759600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>7602400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6979800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6328700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6308400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6486200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>7047200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>8476400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>7117600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>7256700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7067800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6760800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>7306600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6820600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>7016100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>6510600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>6804600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>7425400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>7242800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>7371400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>7338500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>6144100</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5802,130 +5925,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>81913200</v>
+      </c>
+      <c r="E54" s="3">
         <v>83016800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>82258400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82451500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>81186500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78431200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>74443200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>77803200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>73383300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>73898100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>75157900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74270900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>75562600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>72491100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>78923600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>77177100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>113541300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>111268200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100247200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>97637300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>91836400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>93110000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>95141800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>98722800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>110335900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>112320900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>108683200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>117800800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>87378800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>83032800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>76693000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>72176700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>74511100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>72602900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>73538300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>76671300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>75953900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>78000100</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>77797300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>77410100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5968,8 +6097,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6012,740 +6142,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19028800</v>
+      </c>
+      <c r="E57" s="3">
         <v>18763500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4757700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19559400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18697800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17881400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4334200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18057900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16842500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17311600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4735800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17928900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16648700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16429100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>21340300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20620900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18879100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>21806000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22246200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18897400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17013500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>17422600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>18737100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18471700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>20140500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>20379100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>20373700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>20854500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>18380100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>17872700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>18539900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>16125300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>16218300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>27262800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>27351400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>25877500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>25538400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>15844900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>15754100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>15424900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5693200</v>
+      </c>
+      <c r="E58" s="3">
         <v>6660500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4053800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3839000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2808600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2529700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2940800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3773000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4253900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3303900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3583100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5910000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7524400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5271400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5185800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3574000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4242300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5088900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4563500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6041500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6011400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3782600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4406300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5994600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7774600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>9670400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>9434700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11626500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>13933800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11201100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7651300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3574100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4486100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>4449900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3684700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6182400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>8624100</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4924800</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>5437000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>5215800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3849000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4192900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14119800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5278700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6412500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6502700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15029400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6930700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4615400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4449500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13534900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3484000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3921700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3903200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3405200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2616800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25122000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3224300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3187300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2876200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2479200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2972900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3055400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2589800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3272000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3673800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2990800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3624100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3085600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3492300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3514600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2955800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2822200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3098900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3618200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3727700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3386000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3929300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3829200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>3241900</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28571000</v>
+      </c>
+      <c r="E60" s="3">
         <v>29616900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>28790000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28677000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27918900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26913800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27163000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28761600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25711800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25065000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26835500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27322900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28094700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25603700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29931300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>26811700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>48243400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>30119300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>29997000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>27815000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>25504200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24178100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>26198900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>27056200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>31187100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>33723400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>32799100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>36105100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>35399500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>32566000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>29705900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>22655300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>23526600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>34811500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>34654200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>35787700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>37548500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>24699000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>25020300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>23882600</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18577700</v>
+      </c>
+      <c r="E61" s="3">
         <v>18576400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19885600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>20020400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>20967300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21284500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>18324400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17751000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17158500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>19141700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>19367500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>19523800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>19764600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20590900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>22353300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>24724600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>23951500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>36257800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>26070900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25729200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>24377300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>27483800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>27709400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28465100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>33536200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>32932700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>32171800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>35141400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>32013200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>31080200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>26773700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>30553500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>31792800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>18118700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>18604700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>18643800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>15989500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>19225100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>19305500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>20279900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9425500</v>
+      </c>
+      <c r="E62" s="3">
         <v>9194400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9282600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9820700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9708200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9653900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9554700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10147400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9909400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9707200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8957000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8754500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8646500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8875200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13391000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>14487700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>12478100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>16813900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>17132600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>17108200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>16222900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>16393400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>16619700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>18041100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>19362200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>18913600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>18677100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20997400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>15891900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>14898400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>15363400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>14382600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>15283600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>15031500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>15728700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>15941300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>16645600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>26711100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>26936300</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>27983100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6866,8 +7015,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7140,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7110,130 +7265,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>59123000</v>
+      </c>
+      <c r="E66" s="3">
         <v>60011500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60783300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>61277800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61520800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>60790200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58060500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>59772100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55980900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57190100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>58860200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>58871700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>60111100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58496600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65016900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>65466100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>92662800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>91194000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>81168000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>78496700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>73499200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>75383300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>77886900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>81295400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>92616200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>94891500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>93129100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>101142200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>82416100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>77688500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>70934300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>66664000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>69754900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>72692100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>73627000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>74983500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>74896100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>75743100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>76317200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>77228400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7276,8 +7437,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7398,8 +7560,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7520,8 +7685,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7642,8 +7810,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7764,130 +7935,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15210300</v>
+      </c>
+      <c r="E72" s="3">
         <v>15304300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14747000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13463500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12052300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10732700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10975600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>10973100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10847100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10021700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9862700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8563000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8156000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6996000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7625200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5585500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14775900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14140400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13188800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13374600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>12796800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>12191000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>11781700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>11784200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>11691900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11278400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9389700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>10276500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-1219400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-641700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-100400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>102200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-912700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-5742700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-5778100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-3991200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-4617300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-3455300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-4176900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-5409400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8008,8 +8185,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8130,8 +8310,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8252,130 +8435,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>23411200</v>
+      </c>
+      <c r="E76" s="3">
         <v>23573100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22041700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21706100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20264400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18290900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17115100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18775000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18163200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17479600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17000800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16026400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16127600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14622900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13906700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11711000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20878500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20074100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19079200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>19140600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>18337200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17726700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17255000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17427500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17719700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17429400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15554000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16658700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4962700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5344200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5758600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5512600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4756200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-89200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-88700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1687800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1057800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2257000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1480100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>181700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8496,257 +8685,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>577200</v>
+      </c>
+      <c r="E81" s="3">
         <v>2293700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>856000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2705900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1977000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2098200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>518300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-77700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1482400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1321100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>445800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1786500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2063800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1843300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2625700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13199200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1068500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2235600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>949200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1449300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1663600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1279600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>800800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1517600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2950000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2083200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1771600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2196300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1323800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1105100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1604800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1746400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>570100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>709800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-712200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1580800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-234800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1377400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>338400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1064000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8789,76 +8987,77 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>582300</v>
+      </c>
+      <c r="E83" s="3">
         <v>780400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>251600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>718400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>563700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>445800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>535000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>484500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>340600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>582700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-419300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>844600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>881000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>305000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1223300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>804600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>873400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>650100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1223400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>791800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>430500</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>24</v>
@@ -8866,53 +9065,56 @@
       <c r="AA83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC83" s="3">
         <v>258200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>-188200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>726000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1065600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1575000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>907400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>610900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>252100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>618000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>-228300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>892100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>1417800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>429300</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>821700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>251500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9033,8 +9235,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9155,8 +9360,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9277,8 +9485,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9399,8 +9610,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9521,130 +9735,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3569100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1506700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3065900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2986800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2871600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1479300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2915700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2887000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1406600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1209900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4070900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2699300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1660900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>65600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2499700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1690400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2084800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3153600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4773900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3178900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1540700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>394700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4560100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1050300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3597900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1284500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4709200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3559000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1907400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>882700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5440300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2558000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1760800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1115700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3742100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2474300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1314700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1506400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>3938500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>2326800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9687,130 +9907,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-435200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-291800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-771200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-418000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-350700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-268700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-681000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-408800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-381700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-313200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-619000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-364900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-376200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-288300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-751000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-480000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-426000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-601000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-824000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1199000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-180100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-239700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-608000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-356200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-290700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-262200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-654600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-401900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-383100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-295600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-663000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-370700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-365900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-333500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-696500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-485200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-494300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-547800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1002100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-651800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9931,8 +10155,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10053,130 +10280,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1046800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1935800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1255700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2058000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-856300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1478100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1400900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-979800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>973100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-188200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>341400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-599200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1225000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-504800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-708600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5238700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-694900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4457500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-457500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1467900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-220600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-57200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-683100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>3690500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-77200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-504600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-662300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5261700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-545500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-624400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-338700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-479600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-436900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-602600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-583000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-262000</v>
-      </c>
-      <c r="AO94" s="3">
-        <v>-229100</v>
       </c>
       <c r="AP94" s="3">
         <v>-229100</v>
       </c>
+      <c r="AQ94" s="3">
+        <v>-229100</v>
+      </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10219,130 +10452,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>964600</v>
+      </c>
+      <c r="E96" s="3">
         <v>849100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>869400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>873700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>898800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>790700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>766200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>820300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>824000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>717400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>723500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>691900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>707800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>686600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-858200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-902100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1474000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1181100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1205200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1180000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-1372600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-1128100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-1119000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-1154000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-1491300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-1252600</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-1283300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-1330200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-1561300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-1244900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-1233600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-1150300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-1460900</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1201000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-1211700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-1210400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1466000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-1218000</v>
       </c>
       <c r="AO96" s="3">
         <v>-1218000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-1218000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-1215400</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10463,8 +10700,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10585,8 +10825,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10707,370 +10950,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2851300</v>
+      </c>
+      <c r="E100" s="3">
         <v>359200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1152100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1767600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3249800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1108500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1054100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1662000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2001800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1338800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4575300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2150200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>39400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-393400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1755700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1696800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-5720100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9891300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3515500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1729700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2438700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1640900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2572800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5216300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3427100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1400300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3762700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2618000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1224900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>4874300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4287300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2056800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1538400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-365900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-4248100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-846500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1258700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1987000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-2558500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2587500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-35600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-14200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-45600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-24000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-43300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>28100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-72400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-38400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>55400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>25600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>86300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>15800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>60400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>29400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>90500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>14900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-10100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>16100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-41700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-54900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-18300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>55900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-139100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>74200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-53300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>52800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-67200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-30000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-40400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-74300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>14500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>105300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-338300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-67300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>603000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-759500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1270000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1095600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>469500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>199700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>367800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-341000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-206300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-22000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>402800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-870900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>95800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5215700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4239700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8602300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>790800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1117400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1345200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1899700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4904000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3843000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-137100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>302800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>287300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>442000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>660400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-120700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-93100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>203000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-973000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>984800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-601300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-728200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1256200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-412200</v>
       </c>
     </row>
